--- a/DevTools/DataTables/Authoring/DataTables_Authoring.xlsx
+++ b/DevTools/DataTables/Authoring/DataTables_Authoring.xlsx
@@ -5044,9 +5044,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="0.########"/>
     <numFmt numFmtId="165" formatCode="0.########"/>
+    <numFmt numFmtId="166" formatCode="0.########"/>
   </numFmts>
   <fonts count="11">
     <font>
@@ -5192,7 +5193,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -5243,6 +5244,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -9710,10 +9720,6 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0900-000000000000}">
@@ -9950,10 +9956,6 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0A00-000000000000}">
@@ -10376,10 +10378,6 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0B00-000001000000}">
@@ -10785,10 +10783,6 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0C00-000001000000}">
@@ -10814,7 +10808,7 @@
   <sheetPr>
     <tabColor rgb="FF7E57C2"/>
   </sheetPr>
-  <dimension ref="A1:K158"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="35" customWidth="1"/>
@@ -12339,6 +12333,30 @@
       </c>
       <c r="B158" s="9" t="s">
         <v>862</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>ui_p0_cover_bubble_a.text</t>
+        </is>
+      </c>
+      <c r="B159" s="1" t="inlineStr">
+        <is>
+          <t>吃什么</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" spans="1:3">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>ui_p0_cover_bubble_b.text</t>
+        </is>
+      </c>
+      <c r="B160" s="1" t="inlineStr">
+        <is>
+          <t>汪！</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -12474,7 +12492,6 @@
     </row>
   </sheetData>
   <phoneticPr fontId="5" type="noConversion"/>
-  <dataValidations count="0"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
@@ -12647,10 +12664,6 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0200-000000000000}">
@@ -13955,10 +13968,6 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0300-000002000000}">
@@ -14221,10 +14230,6 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0400-000001000000}">
@@ -14458,10 +14463,6 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0500-000001000000}">
@@ -15404,10 +15405,6 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0700-000002000000}">
@@ -15857,10 +15854,6 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
-      <x14:conditionalFormattings>
-      </x14:conditionalFormattings>
-    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" xr:uid="{00000000-0002-0000-0800-000001000000}">
